--- a/samples/exam-underperforming-final/magasins.xlsx
+++ b/samples/exam-underperforming-final/magasins.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
   <si>
     <t>store_id</t>
   </si>
@@ -64,85 +64,82 @@
     <t>S01</t>
   </si>
   <si>
+    <t>Peripherie</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>Reebok|Jordans|New Balance</t>
+  </si>
+  <si>
+    <t>9h/19h</t>
+  </si>
+  <si>
+    <t>open 5/7</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
     <t>Centre-ville</t>
   </si>
   <si>
     <t>Premium</t>
   </si>
   <si>
-    <t>non</t>
-  </si>
-  <si>
-    <t>Reebok</t>
+    <t>Adidas</t>
   </si>
   <si>
     <t>9h/18h</t>
   </si>
   <si>
-    <t>open 5/7</t>
-  </si>
-  <si>
-    <t>S02</t>
-  </si>
-  <si>
-    <t>Peripherie</t>
-  </si>
-  <si>
-    <t>Discount</t>
-  </si>
-  <si>
-    <t>oui</t>
-  </si>
-  <si>
-    <t>Asics|Puma|Nike</t>
+    <t>S03</t>
+  </si>
+  <si>
+    <t>Nike|Puma|Reebok|New Balance</t>
+  </si>
+  <si>
+    <t>S04</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Reebok|New Balance|Jordans</t>
+  </si>
+  <si>
+    <t>open 6/7</t>
+  </si>
+  <si>
+    <t>S05</t>
+  </si>
+  <si>
+    <t>Reebok|Nike|Asics</t>
   </si>
   <si>
     <t>9h/20h</t>
   </si>
   <si>
-    <t>S03</t>
-  </si>
-  <si>
-    <t>Nike|Asics|Adidas</t>
-  </si>
-  <si>
-    <t>S04</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>Adidas|New Balance|Reebok</t>
-  </si>
-  <si>
-    <t>open 6/7</t>
-  </si>
-  <si>
-    <t>S05</t>
-  </si>
-  <si>
-    <t>Jordans|Nike|Adidas</t>
-  </si>
-  <si>
-    <t>9h/19h</t>
-  </si>
-  <si>
     <t>S06</t>
   </si>
   <si>
-    <t>Adidas|Nike|Puma</t>
+    <t>New Balance|Nike|Puma</t>
   </si>
   <si>
     <t>S07</t>
   </si>
   <si>
-    <t>Puma|Adidas|New Balance|Asics</t>
+    <t>New Balance|Reebok|Nike|Adidas|Puma</t>
   </si>
   <si>
     <t>S08</t>
   </si>
   <si>
-    <t>Reebok|New Balance|Jordans|Asics|Adidas</t>
+    <t>Reebok|Puma|Nike|Asics</t>
   </si>
 </sst>
 </file>
@@ -537,7 +534,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="6" max="6" width="37" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
@@ -611,7 +608,7 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -620,7 +617,7 @@
         <v>20</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -629,25 +626,25 @@
         <v>22</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K2">
-        <v>99</v>
+        <v>350</v>
       </c>
       <c r="L2">
-        <v>0.23</v>
+        <v>0.028</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="N2">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="O2">
-        <v>186486</v>
+        <v>27772</v>
       </c>
       <c r="P2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -661,140 +658,140 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
         <v>27</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>737</v>
+        <v>90</v>
       </c>
       <c r="L3">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="M3">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="O3">
-        <v>378081</v>
+        <v>28377</v>
       </c>
       <c r="P3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4">
         <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
       </c>
       <c r="J4">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="K4">
-        <v>459</v>
+        <v>198</v>
       </c>
       <c r="L4">
-        <v>0.17</v>
+        <v>0.023</v>
       </c>
       <c r="M4">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="O4">
-        <v>227067</v>
+        <v>13296</v>
       </c>
       <c r="P4">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
       <c r="D5">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
         <v>33</v>
       </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
       <c r="J5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K5">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="L5">
-        <v>0.22</v>
+        <v>0.043</v>
       </c>
       <c r="M5">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="O5">
-        <v>124291</v>
+        <v>33858</v>
       </c>
       <c r="P5">
         <v>5</v>
@@ -802,75 +799,75 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>153</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>271</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
         <v>36</v>
       </c>
-      <c r="G6">
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>38</v>
+      </c>
+      <c r="K6">
+        <v>418</v>
+      </c>
+      <c r="L6">
+        <v>0.023</v>
+      </c>
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6">
-        <v>64</v>
-      </c>
-      <c r="K6">
-        <v>640</v>
-      </c>
-      <c r="L6">
-        <v>0.17</v>
-      </c>
-      <c r="M6">
-        <v>109</v>
-      </c>
       <c r="N6">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="O6">
-        <v>257856</v>
+        <v>28055</v>
       </c>
       <c r="P6">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
         <v>21</v>
@@ -879,125 +876,125 @@
         <v>22</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="K7">
-        <v>234</v>
+        <v>450</v>
       </c>
       <c r="L7">
-        <v>0.16</v>
+        <v>0.014</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="O7">
-        <v>110074</v>
+        <v>17324</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
       </c>
       <c r="J8">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>180</v>
+        <v>279</v>
       </c>
       <c r="L8">
-        <v>0.17</v>
+        <v>0.024</v>
       </c>
       <c r="M8">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O8">
-        <v>109242</v>
+        <v>19628</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9">
-        <v>305</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9">
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J9">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>710</v>
+        <v>200</v>
       </c>
       <c r="L9">
-        <v>0.15</v>
+        <v>0.054</v>
       </c>
       <c r="M9">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="N9">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="O9">
-        <v>281160</v>
+        <v>47409</v>
       </c>
       <c r="P9">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
